--- a/internal/migration/Defab Thrippunithura/Running_Materials.xlsx
+++ b/internal/migration/Defab Thrippunithura/Running_Materials.xlsx
@@ -1,72 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QMark\defab_erp_backend\internal\migration\Defab Thrippunithura\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4BB6AA6-EF82-4BF3-9732-E3F4ADFF2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Running Material — Trippunithura</t>
+  </si>
+  <si>
+    <t>SL No</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>MRP</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>MRP Excluding GST</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>6114 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>6195 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>4257 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>5126 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>5127 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>6039 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>4258 COTTON LINNING</t>
+  </si>
+  <si>
+    <t>5125 BUTTER CREPE</t>
+  </si>
+  <si>
+    <t>4259 BUTTER CREPE</t>
+  </si>
+  <si>
+    <t>2068 BUTTER CREPE</t>
+  </si>
+  <si>
+    <t>6194 BUTTER CREPE</t>
+  </si>
+  <si>
+    <t>6113 BUTTER CREPE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
+        <fgColor rgb="FFE8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,117 +144,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -478,185 +479,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Running Material — Trippunithura</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SL No</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>MRP</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>MRP Excluding GST</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="n">
+    <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>0326 BF CTN PRNT</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>6669</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2143.8</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>142.86</v>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>0426PLF PRNTD CTN JUTE</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>7235</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>650</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>619.05</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>COTTON VOIL</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>6114</v>
+      </c>
+      <c r="D3" s="2">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2">
+        <v>423.1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6195</v>
+      </c>
+      <c r="D4" s="2">
+        <v>55</v>
+      </c>
+      <c r="E4" s="2">
+        <v>96.5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>455</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="C5" s="2">
+        <v>4257</v>
+      </c>
+      <c r="D5" s="2">
+        <v>55</v>
+      </c>
+      <c r="E5" s="2">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5126</v>
+      </c>
+      <c r="D6" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" s="2">
+        <v>272.14999999999998</v>
+      </c>
+      <c r="F6" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5127</v>
+      </c>
+      <c r="D7" s="2">
+        <v>55</v>
+      </c>
+      <c r="E7" s="2">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6039</v>
+      </c>
+      <c r="D8" s="2">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2">
+        <v>214.7</v>
+      </c>
+      <c r="F8" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4258</v>
+      </c>
+      <c r="D9" s="2">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2">
         <v>11.5</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>433.33</v>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>CTN EMB</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>4243</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>575</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>547.62</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>DYBL CTN HKBA</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1535</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>176.19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8">
+      <c r="F9" s="2">
+        <v>52.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5125</v>
+      </c>
+      <c r="D10" s="2">
+        <v>65</v>
+      </c>
+      <c r="E10" s="2">
+        <v>273.89999999999998</v>
+      </c>
+      <c r="F10" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4259</v>
+      </c>
+      <c r="D11" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" s="2">
+        <v>280.95</v>
+      </c>
+      <c r="F11" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2068</v>
+      </c>
+      <c r="D12" s="2">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2">
+        <v>181.85</v>
+      </c>
+      <c r="F12" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>6194</v>
+      </c>
+      <c r="D13" s="2">
+        <v>65</v>
+      </c>
+      <c r="E13" s="2">
+        <v>148.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6113</v>
+      </c>
+      <c r="D14" s="2">
+        <v>65</v>
+      </c>
+      <c r="E14" s="2">
+        <v>894.25</v>
+      </c>
+      <c r="F14" s="2">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5">
         <f>SUM(E3:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="8" t="n"/>
+        <v>850.75</v>
+      </c>
+      <c r="F15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
